--- a/Config/Datas/Tables/s_升级选项_UpgradeOptionConfig.xlsx
+++ b/Config/Datas/Tables/s_升级选项_UpgradeOptionConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradeOption" sheetId="1" r:id="R712cfae6ff014e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradeOption" sheetId="1" r:id="Rc5565cb7a0424355"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +46,14 @@
       <x:color rgb="FF334E68"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,8 +80,48 @@
         <x:fgColor rgb="FFF5F8FB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -91,11 +137,25 @@
         <x:color rgb="FFD7E0E8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -132,6 +192,57 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -337,380 +448,693 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="21" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="7" t="str">
+      <x:c r="A1" s="24" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="str">
+      <x:c r="B1" s="24" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" s="7" t="str">
+      <x:c r="C1" s="24" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="D1" s="7" t="str">
+      <x:c r="D1" s="24" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="E1" s="7" t="str">
+      <x:c r="E1" s="24" t="str">
         <x:v>type</x:v>
       </x:c>
-      <x:c r="F1" s="7" t="str">
+      <x:c r="F1" s="24" t="str">
         <x:v>targetSkillId</x:v>
       </x:c>
-      <x:c r="G1" s="7" t="str">
+      <x:c r="G1" s="24" t="str">
         <x:v>maxRank</x:v>
       </x:c>
-      <x:c r="H1" s="7" t="str">
-        <x:v>weight</x:v>
-      </x:c>
-      <x:c r="I1" s="7" t="str">
+      <x:c r="H1" s="24" t="str">
         <x:v>modifiers</x:v>
       </x:c>
-      <x:c r="J1" s="7" t="str">
+      <x:c r="I1" s="24" t="str">
         <x:v>healMilli</x:v>
       </x:c>
-      <x:c r="K1" s="7" t="str">
+      <x:c r="J1" s="24" t="str">
         <x:v>iconResourceId</x:v>
       </x:c>
+      <x:c r="K1" t="str">
+        <x:v>runWeaponId</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>runPassiveId</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="9" t="str">
+      <x:c r="A2" s="26" t="str">
         <x:v>##type</x:v>
       </x:c>
-      <x:c r="B2" s="9" t="str">
+      <x:c r="B2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="str">
+      <x:c r="C2" s="26" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="9" t="str">
+      <x:c r="D2" s="26" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="E2" s="9" t="str">
+      <x:c r="E2" s="26" t="str">
         <x:v>EUpgradeOptionType</x:v>
       </x:c>
-      <x:c r="F2" s="9" t="str">
+      <x:c r="F2" s="26" t="str">
         <x:v>int?#ref=TbSkill</x:v>
       </x:c>
-      <x:c r="G2" s="9" t="str">
+      <x:c r="G2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
+      <x:c r="H2" s="26" t="str">
         <x:v>(list#sep=;),RunAttributeModifier</x:v>
       </x:c>
-      <x:c r="J2" s="9" t="str">
+      <x:c r="I2" s="26" t="str">
         <x:v>long?</x:v>
       </x:c>
-      <x:c r="K2" s="9" t="str">
+      <x:c r="J2" s="26" t="str">
         <x:v>int?#ref=TbResource</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="11" t="str">
+      <x:c r="K2" t="str">
+        <x:v>int?#ref=TbRunWeapon</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>int?#ref=TbRunPassive</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="28" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B3" s="11"/>
-      <x:c r="C3" s="11"/>
-      <x:c r="D3" s="11"/>
-      <x:c r="E3" s="11"/>
-      <x:c r="F3" s="11"/>
-      <x:c r="G3" s="11"/>
-      <x:c r="H3" s="11"/>
-      <x:c r="I3" s="11"/>
-      <x:c r="J3" s="11"/>
-      <x:c r="K3" s="11"/>
-    </x:row>
-    <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="13" t="str">
+      <x:c r="B3" s="28"/>
+      <x:c r="C3" s="28"/>
+      <x:c r="D3" s="28"/>
+      <x:c r="E3" s="28"/>
+      <x:c r="F3" s="28"/>
+      <x:c r="G3" s="28"/>
+      <x:c r="H3" s="28"/>
+      <x:c r="I3" s="28"/>
+      <x:c r="J3" s="28"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="30" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
+      <x:c r="B4" s="30" t="str">
         <x:v>选项ID</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
+      <x:c r="C4" s="30" t="str">
         <x:v>显示名称</x:v>
       </x:c>
-      <x:c r="D4" s="13" t="str">
+      <x:c r="D4" s="30" t="str">
         <x:v>显示说明</x:v>
       </x:c>
-      <x:c r="E4" s="13" t="str">
+      <x:c r="E4" s="30" t="str">
         <x:v>选项类型</x:v>
       </x:c>
-      <x:c r="F4" s="13" t="str">
+      <x:c r="F4" s="30" t="str">
         <x:v>目标技能；技能解锁必填</x:v>
       </x:c>
-      <x:c r="G4" s="13" t="str">
+      <x:c r="G4" s="30" t="str">
         <x:v>最大可选次数</x:v>
       </x:c>
-      <x:c r="H4" s="13" t="str">
-        <x:v>正整数抽取权重</x:v>
-      </x:c>
-      <x:c r="I4" s="13" t="str">
+      <x:c r="H4" s="30" t="str">
         <x:v>属性ID:操作:数值</x:v>
       </x:c>
-      <x:c r="J4" s="13" t="str">
-        <x:v>立即恢复量，原单位乘1000</x:v>
-      </x:c>
-      <x:c r="K4" s="13" t="str">
-        <x:v>图标资源；完成UI资源后填写</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="5"/>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="I4" s="30" t="str">
+        <x:v>立即恢复量；原单位乘1000</x:v>
+      </x:c>
+      <x:c r="J4" s="30" t="str">
+        <x:v>图标资源；正式UI资源完成后填写</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>局内武器选项专用引用</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>局内被动选项专用引用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="14"/>
+      <x:c r="B5" s="14" t="n">
         <x:v>40001</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str">
+      <x:c r="C5" s="14" t="str">
         <x:v>解锁 skill_14</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="str">
+      <x:c r="D5" s="14" t="str">
         <x:v>解锁弹道技能 20014</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="str">
+      <x:c r="E5" s="14" t="str">
         <x:v>SkillUnlock</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="14" t="n">
         <x:v>20014</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="n">
+      <x:c r="G5" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="5"/>
-      <x:c r="B6" s="5" t="n">
+      <x:c r="H5" s="14"/>
+      <x:c r="I5" s="14"/>
+      <x:c r="J5" s="14"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="14"/>
+      <x:c r="B6" s="14" t="n">
         <x:v>40002</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str">
+      <x:c r="C6" s="14" t="str">
         <x:v>解锁 skill_32</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="str">
+      <x:c r="D6" s="14" t="str">
         <x:v>解锁弹道技能 20032</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="str">
+      <x:c r="E6" s="14" t="str">
         <x:v>SkillUnlock</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="n">
+      <x:c r="F6" s="14" t="n">
         <x:v>20032</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="n">
+      <x:c r="G6" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H6" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5"/>
-      <x:c r="K6" s="5"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="5"/>
-      <x:c r="B7" s="5" t="n">
+      <x:c r="H6" s="14"/>
+      <x:c r="I6" s="14"/>
+      <x:c r="J6" s="14"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="14"/>
+      <x:c r="B7" s="14" t="n">
         <x:v>40003</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str">
+      <x:c r="C7" s="14" t="str">
         <x:v>解锁 skill_28</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="str">
+      <x:c r="D7" s="14" t="str">
         <x:v>解锁目标位置群体技能 20028</x:v>
       </x:c>
-      <x:c r="E7" s="5" t="str">
+      <x:c r="E7" s="14" t="str">
         <x:v>SkillUnlock</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="n">
+      <x:c r="F7" s="14" t="n">
         <x:v>20028</x:v>
       </x:c>
-      <x:c r="G7" s="5" t="n">
+      <x:c r="G7" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I7" s="5"/>
-      <x:c r="J7" s="5"/>
-      <x:c r="K7" s="5"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="5"/>
-      <x:c r="B8" s="5" t="n">
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="14"/>
+      <x:c r="J7" s="14"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="14"/>
+      <x:c r="B8" s="14" t="n">
         <x:v>40004</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="str">
+      <x:c r="C8" s="14" t="str">
         <x:v>解锁 skill_43</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="str">
+      <x:c r="D8" s="14" t="str">
         <x:v>解锁目标位置群体技能 20043</x:v>
       </x:c>
-      <x:c r="E8" s="5" t="str">
+      <x:c r="E8" s="14" t="str">
         <x:v>SkillUnlock</x:v>
       </x:c>
-      <x:c r="F8" s="5" t="n">
+      <x:c r="F8" s="14" t="n">
         <x:v>20043</x:v>
       </x:c>
-      <x:c r="G8" s="5" t="n">
+      <x:c r="G8" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H8" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I8" s="5"/>
-      <x:c r="J8" s="5"/>
-      <x:c r="K8" s="5"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="5"/>
-      <x:c r="B9" s="5" t="n">
+      <x:c r="H8" s="14"/>
+      <x:c r="I8" s="14"/>
+      <x:c r="J8" s="14"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="14"/>
+      <x:c r="B9" s="14" t="n">
         <x:v>40005</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="str">
+      <x:c r="C9" s="14" t="str">
         <x:v>攻击强化</x:v>
       </x:c>
-      <x:c r="D9" s="5" t="str">
+      <x:c r="D9" s="14" t="str">
         <x:v>攻击提高 5%</x:v>
       </x:c>
-      <x:c r="E9" s="5" t="str">
+      <x:c r="E9" s="14" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="F9" s="5"/>
-      <x:c r="G9" s="5" t="n">
+      <x:c r="F9" s="14"/>
+      <x:c r="G9" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H9" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="str">
+      <x:c r="H9" s="14" t="str">
         <x:v>2:AddPercent:50</x:v>
       </x:c>
-      <x:c r="J9" s="5"/>
-      <x:c r="K9" s="5"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="5"/>
-      <x:c r="B10" s="5" t="n">
+      <x:c r="I9" s="14"/>
+      <x:c r="J9" s="14"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="14"/>
+      <x:c r="B10" s="14" t="n">
         <x:v>40006</x:v>
       </x:c>
-      <x:c r="C10" s="5" t="str">
+      <x:c r="C10" s="14" t="str">
         <x:v>生命强化</x:v>
       </x:c>
-      <x:c r="D10" s="5" t="str">
+      <x:c r="D10" s="14" t="str">
         <x:v>最大生命提高 5%</x:v>
       </x:c>
-      <x:c r="E10" s="5" t="str">
+      <x:c r="E10" s="14" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="F10" s="5"/>
-      <x:c r="G10" s="5" t="n">
+      <x:c r="F10" s="14"/>
+      <x:c r="G10" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H10" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="str">
+      <x:c r="H10" s="14" t="str">
         <x:v>1:AddPercent:50</x:v>
       </x:c>
-      <x:c r="J10" s="5"/>
-      <x:c r="K10" s="5"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="5"/>
-      <x:c r="B11" s="5" t="n">
+      <x:c r="I10" s="14"/>
+      <x:c r="J10" s="14"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="14"/>
+      <x:c r="B11" s="14" t="n">
         <x:v>40007</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="str">
+      <x:c r="C11" s="14" t="str">
         <x:v>移动强化</x:v>
       </x:c>
-      <x:c r="D11" s="5" t="str">
+      <x:c r="D11" s="14" t="str">
         <x:v>移动速度提高 3%</x:v>
       </x:c>
-      <x:c r="E11" s="5" t="str">
+      <x:c r="E11" s="14" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="5" t="n">
+      <x:c r="F11" s="14"/>
+      <x:c r="G11" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H11" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I11" s="5" t="str">
+      <x:c r="H11" s="14" t="str">
         <x:v>4:AddPercent:30</x:v>
       </x:c>
-      <x:c r="J11" s="5"/>
-      <x:c r="K11" s="5"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="5"/>
-      <x:c r="B12" s="5" t="n">
+      <x:c r="I11" s="14"/>
+      <x:c r="J11" s="14"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="14"/>
+      <x:c r="B12" s="14" t="n">
         <x:v>40008</x:v>
       </x:c>
-      <x:c r="C12" s="5" t="str">
+      <x:c r="C12" s="14" t="str">
         <x:v>攻速强化</x:v>
       </x:c>
-      <x:c r="D12" s="5" t="str">
+      <x:c r="D12" s="14" t="str">
         <x:v>攻击速度提高 3%</x:v>
       </x:c>
-      <x:c r="E12" s="5" t="str">
+      <x:c r="E12" s="14" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="5" t="n">
+      <x:c r="F12" s="14"/>
+      <x:c r="G12" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H12" s="5" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I12" s="5" t="str">
+      <x:c r="H12" s="14" t="str">
         <x:v>5:AddPercent:30</x:v>
       </x:c>
-      <x:c r="J12" s="5"/>
-      <x:c r="K12" s="5"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="5"/>
-      <x:c r="B13" s="5" t="n">
+      <x:c r="I12" s="14"/>
+      <x:c r="J12" s="14"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="14"/>
+      <x:c r="B13" s="14" t="n">
         <x:v>40009</x:v>
       </x:c>
-      <x:c r="C13" s="5" t="str">
+      <x:c r="C13" s="14" t="str">
         <x:v>生命恢复</x:v>
       </x:c>
-      <x:c r="D13" s="5" t="str">
+      <x:c r="D13" s="14" t="str">
         <x:v>立即恢复 20 点生命</x:v>
       </x:c>
-      <x:c r="E13" s="5" t="str">
+      <x:c r="E13" s="14" t="str">
         <x:v>Heal</x:v>
       </x:c>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5" t="n">
+      <x:c r="F13" s="14"/>
+      <x:c r="G13" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H13" s="5" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="I13" s="5"/>
-      <x:c r="J13" s="5" t="n">
+      <x:c r="H13" s="14"/>
+      <x:c r="I13" s="14" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="K13" s="5"/>
+      <x:c r="J13" s="14"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="n">
+        <x:v>41001</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>追星飞刃</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>单发追踪目标方向；超武改为环射并穿透；重复获得升星</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>RunWeapon</x:v>
+      </x:c>
+      <x:c r="F14"/>
+      <x:c r="G14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14" t="n">
+        <x:v>50001</x:v>
+      </x:c>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15" t="n">
+        <x:v>41002</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>焚天炎符</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>扇形三发；超武扇面扩大并在命中处爆发；重复获得升星</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>RunWeapon</x:v>
+      </x:c>
+      <x:c r="F15"/>
+      <x:c r="G15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15" t="n">
+        <x:v>50002</x:v>
+      </x:c>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16" t="n">
+        <x:v>41003</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>落雷法印</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>目标位置瞬时落雷；超武连续打击不同目标落点；重复获得升星</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>RunWeapon</x:v>
+      </x:c>
+      <x:c r="F16"/>
+      <x:c r="G16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16" t="n">
+        <x:v>50003</x:v>
+      </x:c>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17" t="n">
+        <x:v>41004</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>寒霜灵阵</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>固定位置持续脉冲；超武扩大范围并加快持续脉冲；重复获得升星</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>RunWeapon</x:v>
+      </x:c>
+      <x:c r="F17"/>
+      <x:c r="G17" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17" t="n">
+        <x:v>50004</x:v>
+      </x:c>
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18" t="n">
+        <x:v>41005</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>护体罡环</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>随身护体脉冲；超武改为双环覆盖；重复获得升星</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>RunWeapon</x:v>
+      </x:c>
+      <x:c r="F18"/>
+      <x:c r="G18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18" t="n">
+        <x:v>50005</x:v>
+      </x:c>
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="n">
+        <x:v>41006</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>连锁灵梭</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>命中后跳向未命中目标；超武增加跳数并扩大连锁距离；重复获得升星</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>RunWeapon</x:v>
+      </x:c>
+      <x:c r="F19"/>
+      <x:c r="G19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19" t="n">
+        <x:v>50006</x:v>
+      </x:c>
+      <x:c r="L19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20" t="n">
+        <x:v>41007</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>锋锐真诀</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>获得或提升被动：攻击；占独立被动槽</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>RunPassive</x:v>
+      </x:c>
+      <x:c r="F20"/>
+      <x:c r="G20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20" t="n">
+        <x:v>51001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21" t="n">
+        <x:v>41008</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>疾攻心法</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>获得或提升被动：攻速；占独立被动槽</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>RunPassive</x:v>
+      </x:c>
+      <x:c r="F21"/>
+      <x:c r="G21" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21" t="n">
+        <x:v>51002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22" t="n">
+        <x:v>41009</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>广域灵纹</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>获得或提升被动：技能范围；占独立被动槽</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>RunPassive</x:v>
+      </x:c>
+      <x:c r="F22"/>
+      <x:c r="G22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22" t="n">
+        <x:v>51003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23" t="n">
+        <x:v>41010</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>长生诀</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>获得或提升被动：最大生命；占独立被动槽</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>RunPassive</x:v>
+      </x:c>
+      <x:c r="F23"/>
+      <x:c r="G23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23" t="n">
+        <x:v>51004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24" t="n">
+        <x:v>41011</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>御风步</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>获得或提升被动：移动速度；占独立被动槽</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>RunPassive</x:v>
+      </x:c>
+      <x:c r="F24"/>
+      <x:c r="G24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H24"/>
+      <x:c r="I24"/>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
+      <x:c r="L24" t="n">
+        <x:v>51005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25" t="n">
+        <x:v>41012</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>磐石护体</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>获得或提升被动：防御；占独立被动槽</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>RunPassive</x:v>
+      </x:c>
+      <x:c r="F25"/>
+      <x:c r="G25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H25"/>
+      <x:c r="I25"/>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
+      <x:c r="L25" t="n">
+        <x:v>51006</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/s_升级选项_UpgradeOptionConfig.xlsx
+++ b/Config/Datas/Tables/s_升级选项_UpgradeOptionConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradeOption" sheetId="1" r:id="Rc5565cb7a0424355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradeOption" sheetId="1" r:id="R76bafe0dceef4e7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1136,6 +1136,54 @@
         <x:v>51006</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26" t="n">
+        <x:v>42001</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>破围</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>自动反击范围增加15%；不增加伤害段，不改变蓄能规则。</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>MechanismModifier</x:v>
+      </x:c>
+      <x:c r="F26"/>
+      <x:c r="G26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27" t="n">
+        <x:v>42002</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>交织</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>重叠引爆有效伤害敌人后移速提高15%，持续2秒；只刷新、不叠加。</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>MechanismModifier</x:v>
+      </x:c>
+      <x:c r="F27"/>
+      <x:c r="G27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
